--- a/aftersun_Clinic_Data_Template.xlsx
+++ b/aftersun_Clinic_Data_Template.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/synctrueinc./Desktop/aftersun_data_analysis/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329E81FA-E114-5942-9D77-68FB73DF2C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Clinic Data" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Scoring Rubric" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="STI Reference" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Phone Script" sheetId="4" r:id="rId7"/>
+    <sheet name="Clinic Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Scoring Rubric" sheetId="2" r:id="rId2"/>
+    <sheet name="STI Reference" sheetId="3" r:id="rId3"/>
+    <sheet name="Phone Script" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="GG/VvvoDH8Az3d8Nt/VcrvK2mYsX5Mbjh2gkcB8Wj/s="/>
@@ -331,9 +340,6 @@
     <t>매독, 헤르페스1/2, 임질, 마이코플라즈마호미니스, 마이코플라즈마제니탈리움, 칸디다, 트리코모나스, 클라미디아, 가드넬라, 유레아플라즈마 = STI 12종 모두 검사 가능</t>
   </si>
   <si>
-    <t>30000, 170000(비보험)</t>
-  </si>
-  <si>
     <t>없음</t>
   </si>
   <si>
@@ -475,9 +481,6 @@
     <t>2-3일, 당일 결과 확인</t>
   </si>
   <si>
-    <t>30000원, 3-40000</t>
-  </si>
-  <si>
     <t>월금 09:30-20:00, 화수목 09:30-19:00, 토 09:30-13:00</t>
   </si>
   <si>
@@ -499,9 +502,6 @@
     <t>3-4일</t>
   </si>
   <si>
-    <t>소변 40000원, 피 1,20000원, 매독/에이즈 20000원, 20000, HPV 70000</t>
-  </si>
-  <si>
     <t>매독, 면봉, 에이즈만 비급여</t>
   </si>
   <si>
@@ -532,9 +532,6 @@
     <t>평일 기준 5일</t>
   </si>
   <si>
-    <t>약 80,000원</t>
-  </si>
-  <si>
     <t>평일 10:00-19:00, 토 10:00-18:00, 수요일 휴무</t>
   </si>
   <si>
@@ -553,9 +550,6 @@
     <t>1-2일</t>
   </si>
   <si>
-    <t>소변 36000원, 혈액 2-30000원</t>
-  </si>
-  <si>
     <t>월화목금, 09:00-18:30, 수토 09:00-13:00</t>
   </si>
   <si>
@@ -607,9 +601,6 @@
     <t>12종을 비롯한 보편적인 것 모두</t>
   </si>
   <si>
-    <t>소변 40000원, 20000-</t>
-  </si>
-  <si>
     <t>평일 09:30-18:30 (목 09:30-20:00)</t>
   </si>
   <si>
@@ -631,9 +622,6 @@
     <t>5-7일</t>
   </si>
   <si>
-    <t>70000-80000원</t>
-  </si>
-  <si>
     <t>평일 09:00-17:20, 토 09:00-15:20</t>
   </si>
   <si>
@@ -658,9 +646,6 @@
     <t>2-3일, 최대 5일</t>
   </si>
   <si>
-    <t>소변 40000원, 피부 5~10, 혈액 2~3만원</t>
-  </si>
-  <si>
     <t>평일 09:30-18:30 (월 09:30-19:30), 토 09:30-14:30</t>
   </si>
   <si>
@@ -710,9 +695,6 @@
   </si>
   <si>
     <t>2-3일 (주말 제외)</t>
-  </si>
-  <si>
-    <t>2-30000원, 11만원</t>
   </si>
   <si>
     <t>월 09:00-18:00, 화수목금 09:00-19:30, 토 09:00-15:00, 일 09:00-13:00</t>
@@ -1159,88 +1141,138 @@
   </si>
   <si>
     <t>• 통화 날짜를 last_verified 컬럼에 기록하기</t>
+  </si>
+  <si>
+    <t>30000원, 30000~40000</t>
+  </si>
+  <si>
+    <t>30000, 170000</t>
+  </si>
+  <si>
+    <t>소변 40000원, 피 10000~20000원, 매독/에이즈 20000원, HPV 70000원</t>
+  </si>
+  <si>
+    <t>소변 36000원, 혈액 20000~30000원</t>
+  </si>
+  <si>
+    <t>소변 40000원, 혈액 20000원</t>
+  </si>
+  <si>
+    <t>70000~80000원</t>
+  </si>
+  <si>
+    <t>소변 40000원, 피부 50000~100000, 혈액 20000~30000원</t>
+  </si>
+  <si>
+    <t>약 80000원</t>
+  </si>
+  <si>
+    <t>20000~30000원, 110000원</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF0F6E56"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF888780"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF424242"/>
       <name val="-apple-system"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF444444"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFD4537E"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1248,7 +1280,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1312,19 +1344,28 @@
     </fill>
   </fills>
   <borders count="6">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFD3D1C7"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FFD3D1C7"/>
       </top>
       <bottom style="thin">
         <color rgb="FFD3D1C7"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FFD3D1C7"/>
       </right>
@@ -1334,14 +1375,18 @@
       <bottom style="thin">
         <color rgb="FFD3D1C7"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FFD3D1C7"/>
       </top>
       <bottom style="thin">
         <color rgb="FFD3D1C7"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1356,108 +1401,83 @@
       <bottom style="thin">
         <color rgb="FFD3D1C7"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="9" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1647,2123 +1667,2123 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AB1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.0"/>
-    <col customWidth="1" min="2" max="2" width="22.0"/>
-    <col customWidth="1" min="3" max="3" width="10.0"/>
-    <col customWidth="1" min="4" max="4" width="16.0"/>
-    <col customWidth="1" min="5" max="5" width="20.14"/>
-    <col customWidth="1" min="6" max="6" width="17.86"/>
-    <col customWidth="1" min="7" max="7" width="16.71"/>
-    <col customWidth="1" min="8" max="8" width="18.0"/>
-    <col customWidth="1" min="9" max="9" width="14.0"/>
-    <col customWidth="1" min="10" max="10" width="20.0"/>
-    <col customWidth="1" min="11" max="11" width="35.0"/>
-    <col customWidth="1" min="12" max="12" width="10.0"/>
-    <col customWidth="1" min="13" max="15" width="12.0"/>
-    <col customWidth="1" min="16" max="16" width="14.0"/>
-    <col customWidth="1" min="17" max="18" width="12.0"/>
-    <col customWidth="1" min="19" max="19" width="14.0"/>
-    <col customWidth="1" min="20" max="20" width="20.0"/>
-    <col customWidth="1" min="21" max="21" width="12.0"/>
-    <col customWidth="1" min="22" max="22" width="18.0"/>
-    <col customWidth="1" min="23" max="26" width="12.0"/>
-    <col customWidth="1" min="27" max="27" width="24.0"/>
-    <col customWidth="1" min="28" max="28" width="14.0"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="35" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="18" width="12" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="23" max="26" width="12" customWidth="1"/>
+    <col min="27" max="27" width="24" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:28" ht="30" customHeight="1">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="19"/>
+      <c r="E1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="1" t="s">
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="1" t="s">
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="1" t="s">
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="1" t="s">
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="1" t="s">
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="AB1" s="2"/>
-    </row>
-    <row r="2" ht="45.0" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="AB1" s="19"/>
+    </row>
+    <row r="2" spans="1:28" ht="45" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="U2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="V2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Y2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="Z2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AA2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AB2" s="4" t="s">
+      <c r="AB2" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="X3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Y3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="Z3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AA3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AB3" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:28" ht="28">
+      <c r="A4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="8">
-        <v>8.0</v>
-      </c>
-      <c r="M4" s="8" t="s">
+      <c r="L4" s="3">
+        <v>8</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="O4" s="10">
-        <v>7.0</v>
-      </c>
-      <c r="P4" s="8">
-        <v>55000.0</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="R4" s="8" t="s">
+      <c r="O4" s="3">
+        <v>7</v>
+      </c>
+      <c r="P4" s="3">
+        <v>55000</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="S4" s="8">
-        <v>35000.0</v>
-      </c>
-      <c r="T4" s="9" t="s">
+      <c r="S4" s="3">
+        <v>35000</v>
+      </c>
+      <c r="T4" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="U4" s="8" t="s">
+      <c r="U4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="V4" s="9" t="s">
+      <c r="V4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="W4" s="8" t="s">
+      <c r="W4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="X4" s="8" t="s">
+      <c r="X4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="Y4" s="8" t="s">
+      <c r="Y4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="Z4" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA4" s="9" t="s">
+      <c r="Z4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA4" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AB4" s="8" t="s">
+      <c r="AB4" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:28" ht="28">
+      <c r="A5" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="8" t="s">
+      <c r="H5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="L5" s="8">
-        <v>4.0</v>
-      </c>
-      <c r="M5" s="8" t="s">
+      <c r="L5" s="3">
+        <v>4</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="O5" s="10">
-        <v>14.0</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0.0</v>
-      </c>
-      <c r="Q5" s="8" t="s">
+      <c r="O5" s="3">
+        <v>14</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="R5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="S5" s="8" t="s">
+      <c r="R5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="T5" s="9" t="s">
+      <c r="T5" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="U5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="V5" s="9" t="s">
+      <c r="U5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="V5" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="W5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="X5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA5" s="9" t="s">
+      <c r="W5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="AB5" s="8" t="s">
+      <c r="AB5" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:28">
+      <c r="A6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="11" t="s">
+      <c r="F6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="11" t="s">
+      <c r="H6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="L6" s="11">
-        <v>12.0</v>
-      </c>
-      <c r="M6" s="11" t="s">
+      <c r="L6" s="5">
+        <v>12</v>
+      </c>
+      <c r="M6" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="N6" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="11">
-        <v>7.0</v>
-      </c>
-      <c r="P6" s="11" t="s">
+      <c r="N6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="5">
+        <v>7</v>
+      </c>
+      <c r="P6" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S6" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="T6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="W6" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="R6" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S6" s="11" t="s">
+      <c r="X6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="A7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L7" s="5">
+        <v>4</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="O7" s="5">
+        <v>7</v>
+      </c>
+      <c r="P7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T7" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="U7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB7" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="A8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L8" s="5">
+        <v>3</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5">
+        <v>14</v>
+      </c>
+      <c r="P8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB8" s="6">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="A9" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L9" s="5">
+        <v>12</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB9" s="6">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="A10" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB10" s="6">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="A11" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="L11" s="5">
+        <v>3</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="O11" s="5">
+        <v>7</v>
+      </c>
+      <c r="P11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="U11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB11" s="6">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
+      <c r="A12" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T12" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="U12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="W12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA12" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB12" s="6">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="A13" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="S13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T13" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="T6" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="U6" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="V6" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="W6" s="11" t="s">
+      <c r="U13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="W13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z13" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB13" s="6">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
+      <c r="A14" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="L14" s="5">
+        <v>14</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="N14" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="X6" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y6" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z6" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA6" s="11" t="s">
+      <c r="O14" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S14" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T14" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="U14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="V14" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="W14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="X14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA14" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB14" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28">
+      <c r="A15" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="P15" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q15" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S15" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T15" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="U15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="V15" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="W15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="X15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA15" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB15" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
+      <c r="A16" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T16" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="U16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="V16" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="W16" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="X16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA16" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="AB6" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="AB16" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" ht="28">
+      <c r="A17" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L17" s="5">
+        <v>15</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="P17" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S17" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T17" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="U17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="V17" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="W17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="X17" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y17" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA17" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB17" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28">
+      <c r="A18" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="F18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="L18" s="5">
+        <v>3</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="P18" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T18" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="U18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V18" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="W18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA18" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB18" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28">
+      <c r="A19" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="L19" s="5">
+        <v>3</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T19" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="U19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V19" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="W19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA19" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB19" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28">
+      <c r="A20" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="P20" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="T20" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="U20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V20" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="W20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z20" s="5"/>
+      <c r="AA20" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB20" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="15.75" customHeight="1">
+      <c r="A21" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="J21" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="L21" s="5">
+        <v>6</v>
+      </c>
+      <c r="M21" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="N21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="P21" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="R21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S21" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T21" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="U21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="V21" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="W21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="X21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA21" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB21" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" ht="15.75" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J7" s="11" t="s">
+      <c r="H22" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K22" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T22" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="U22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="V22" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="W22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="X22" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="L7" s="11">
-        <v>4.0</v>
-      </c>
-      <c r="M7" s="11" t="s">
+      <c r="Y22" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA22" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB22" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" ht="15.75" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="R23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="S23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="T23" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="U23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="V23" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="W23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="X23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA23" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB23" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" ht="15.75" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="L24" s="5">
+        <v>3</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="P24" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S24" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T24" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="N7" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="O7" s="11">
-        <v>7.0</v>
-      </c>
-      <c r="P7" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="Q7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="R7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S7" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T7" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="U7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="V7" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="W7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="X7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z7" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA7" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB7" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" s="11" t="s">
+      <c r="U24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V24" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="W24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA24" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB24" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" ht="15.75" customHeight="1">
+      <c r="A25" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="L8" s="11">
-        <v>3.0</v>
-      </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="11">
-        <v>14.0</v>
-      </c>
-      <c r="P8" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="Q8" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="R8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S8" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T8" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="U8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="V8" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="W8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="X8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA8" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB8" s="12">
-        <v>46144.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="11" t="s">
+      <c r="G25" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="L9" s="11">
-        <v>12.0</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="N9" s="11" t="s">
+      <c r="J25" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="M25" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="O9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="P9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="R9" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S9" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="U9" s="11" t="s">
+      <c r="N25" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="V9" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W9" s="11" t="s">
+      <c r="O25" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q25" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="X9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA9" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB9" s="12">
-        <v>46144.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="M10" s="11" t="s">
+      <c r="R25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="T25" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="U25" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="N10" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q10" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="R10" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S10" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T10" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="U10" s="11" t="s">
+      <c r="V25" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="W25" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="V10" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="W10" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="X10" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z10" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA10" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB10" s="12">
-        <v>46144.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="L11" s="11">
-        <v>3.0</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="N11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="O11" s="11">
-        <v>7.0</v>
-      </c>
-      <c r="P11" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="R11" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S11" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T11" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="U11" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="V11" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="W11" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="X11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA11" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB11" s="12">
-        <v>46144.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="L12" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="O12" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q12" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="R12" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="S12" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T12" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="U12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="V12" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="W12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="X12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA12" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="AB12" s="12">
-        <v>46144.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="P13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="R13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="S13" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T13" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="U13" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="V13" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="W13" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="X13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA13" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB13" s="12">
-        <v>46144.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="L14" s="11">
-        <v>14.0</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="N14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="P14" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="R14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S14" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T14" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="U14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V14" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="W14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="X14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA14" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB14" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="N15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="P15" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q15" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="R15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S15" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T15" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="U15" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V15" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="W15" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="X15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA15" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB15" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="N16" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="O16" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="P16" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S16" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T16" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="U16" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V16" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="X16" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y16" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z16" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA16" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB16" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="L17" s="11">
-        <v>15.0</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="N17" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="O17" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="P17" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q17" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="R17" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S17" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T17" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="U17" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V17" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="W17" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="X17" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y17" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z17" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA17" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB17" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="L18" s="11">
-        <v>3.0</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="N18" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="O18" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="P18" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="Q18" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="R18" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S18" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T18" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="U18" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="V18" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="W18" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="X18" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y18" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z18" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA18" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB18" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="L19" s="11">
-        <v>3.0</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="N19" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="O19" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="P19" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="R19" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S19" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T19" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="U19" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="V19" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="W19" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="X19" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y19" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z19" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA19" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB19" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="L20" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="N20" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="P20" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="T20" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="U20" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="V20" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="W20" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="X20" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y20" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z20" s="13"/>
-      <c r="AA20" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="AB20" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="L21" s="11">
-        <v>6.0</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="N21" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="O21" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="P21" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q21" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="R21" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S21" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T21" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="U21" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V21" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="W21" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="X21" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y21" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z21" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA21" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="AB21" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="N22" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="O22" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="P22" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S22" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T22" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="U22" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V22" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="X22" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y22" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z22" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA22" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB22" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="P23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="R23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="S23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="T23" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="U23" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V23" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="W23" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="X23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z23" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AA23" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="AB23" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="L24" s="11">
-        <v>3.0</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="N24" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="O24" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="P24" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="Q24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="R24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S24" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T24" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="U24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="V24" s="11" t="s">
+      <c r="X25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA25" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="W24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="X24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA24" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB24" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="O25" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="P25" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q25" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="R25" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="S25" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="T25" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="U25" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V25" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="W25" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="X25" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y25" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z25" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA25" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="AB25" s="12">
-        <v>46136.0</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+      <c r="AB25" s="6">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -4734,548 +4754,544 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="P1:S1"/>
-    <mergeCell ref="T1:W1"/>
-    <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA1:AB1"/>
   </mergeCells>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="E6:F25 H6:H25 M6:N25 Q6:R25 U6:U25 W6:Z25">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" sqref="E6:F25 H6:H25 M6:N25 Q6:R25 U6:U25 W6:Z25" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Y,N,Unknown,Only HIV"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G6:G25">
+    <dataValidation type="list" allowBlank="1" sqref="G6:G25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"online,phone,walk_in,online+phone,phone+walk_in,all"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D6:D22 D24:D25">
+    <dataValidation type="list" allowBlank="1" sqref="D6:D22 D24:D25" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"standalone_sti,dermatology,urology,obstetrics,general_hospital,public_health"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I6:I25">
+    <dataValidation type="list" allowBlank="1" sqref="I6:I25" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"app,phone,in_person,online_portal,mail,app+phone,mail+online"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D23">
+    <dataValidation type="list" allowBlank="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"standalone_sti,dermatology,urology,obstetrics,general_hospital,public_health,andrology"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.0"/>
-    <col customWidth="1" min="2" max="2" width="22.0"/>
-    <col customWidth="1" min="3" max="3" width="20.0"/>
-    <col customWidth="1" min="4" max="4" width="18.0"/>
-    <col customWidth="1" min="5" max="5" width="36.0"/>
-    <col customWidth="1" min="6" max="6" width="18.0"/>
-    <col customWidth="1" min="7" max="7" width="16.0"/>
-    <col customWidth="1" min="8" max="26" width="8.71"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:7" ht="30">
+      <c r="A1" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="E2" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="F2" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="G2" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="E1" s="17" t="s">
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="C3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="F3" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="18" t="s">
+      <c r="C4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="E4" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="19" t="s">
+      <c r="F4" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="C5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" ht="28">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="C6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19" t="s">
+      <c r="F6" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="19" t="s">
+      <c r="C7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="G3" s="19"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="19" t="s">
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="B8" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="C8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="G4" s="19"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19" t="s">
+      <c r="E8" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="F8" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="G5" s="19"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19" t="s">
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" ht="28">
+      <c r="A17" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A22" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="G6" s="19"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="G7" s="19"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="G9" s="19"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="G10" s="19"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="G11" s="19"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="G12" s="19"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="G14" s="19"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="G15" s="19"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="G16" s="19"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="G18" s="19"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="G19" s="19"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="G21" s="19"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="G23" s="19"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="G24" s="19"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -6245,246 +6261,242 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="18.0"/>
-    <col customWidth="1" min="3" max="3" width="22.0"/>
-    <col customWidth="1" min="4" max="4" width="26.0"/>
-    <col customWidth="1" min="5" max="5" width="30.0"/>
-    <col customWidth="1" min="6" max="26" width="8.71"/>
+    <col min="1" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="20" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="B3" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="C3" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="D3" s="7" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="19" t="s">
+      <c r="E3" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="B2" s="19" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="42">
+      <c r="A4" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="B4" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="C4" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="D4" s="7" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="s">
+      <c r="E4" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="B3" s="19" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="28">
+      <c r="A5" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="B5" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="C5" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="E3" s="14" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="19" t="s">
+      <c r="B6" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="C6" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D6" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E6" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="E4" s="14" t="s">
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="s">
+      <c r="B7" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="C7" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="E5" s="14" t="s">
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="7" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="s">
+      <c r="B8" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="C8" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="D8" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="E8" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="E6" s="19" t="s">
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="7" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="s">
+      <c r="B9" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="C9" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>317</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="D9" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="s">
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B10" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C10" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D10" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E10" s="7" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="19" t="s">
+    <row r="11" spans="1:5">
+      <c r="A11" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B11" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C11" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D11" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="s">
+      <c r="E11" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="B10" s="19" t="s">
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="B12" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="C12" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="D12" s="7" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="s">
+      <c r="E12" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B11" s="19" t="s">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="B13" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="C13" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="D13" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>341</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="s">
-        <v>342</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>343</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>349</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -7468,148 +7480,144 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:A1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="80.0"/>
-    <col customWidth="1" min="2" max="26" width="8.71"/>
+    <col min="1" max="1" width="80" customWidth="1"/>
+    <col min="2" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:1" ht="18">
+      <c r="A1" s="13" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="14"/>
+    </row>
+    <row r="3" spans="1:1" ht="16">
+      <c r="A3" s="14" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="14"/>
+    </row>
+    <row r="5" spans="1:1" ht="16">
+      <c r="A5" s="15" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="14"/>
+    </row>
+    <row r="7" spans="1:1" ht="16">
+      <c r="A7" s="14" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="16">
+      <c r="A8" s="14" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="16">
+      <c r="A9" s="14" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="16">
+      <c r="A10" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="16">
+      <c r="A11" s="14" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="16">
+      <c r="A12" s="14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="16">
+      <c r="A13" s="14" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="22"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="22" t="s">
+    <row r="14" spans="1:1" ht="16">
+      <c r="A14" s="14" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="22"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="s">
+    <row r="15" spans="1:1" ht="16">
+      <c r="A15" s="14" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="22"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="22" t="s">
+    <row r="16" spans="1:1" ht="16">
+      <c r="A16" s="14" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="22" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" s="14"/>
+    </row>
+    <row r="18" spans="1:1" ht="16">
+      <c r="A18" s="14" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="22" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="14"/>
+    </row>
+    <row r="20" spans="1:1" ht="16">
+      <c r="A20" s="15" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="22" t="s">
+    <row r="21" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A21" s="14"/>
+    </row>
+    <row r="22" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A22" s="14" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="22" t="s">
+    <row r="23" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A23" s="14" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="22" t="s">
+    <row r="24" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A24" s="14" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="22" t="s">
+    <row r="25" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A25" s="14" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="22" t="s">
+    <row r="26" spans="1:1" ht="15.75" customHeight="1">
+      <c r="A26" s="14" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="22" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="22" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="22"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="22"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="22" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="22" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="22" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="22" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="22" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:1" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -8579,9 +8587,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/aftersun_Clinic_Data_Template.xlsx
+++ b/aftersun_Clinic_Data_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/synctrueinc./Desktop/aftersun_data_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329E81FA-E114-5942-9D77-68FB73DF2C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB295FED-010F-D047-A297-CFFAF0C81EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2137,7 +2137,7 @@
       <c r="O6" s="5">
         <v>7</v>
       </c>
-      <c r="P6" s="16" t="s">
+      <c r="P6" s="5" t="s">
         <v>363</v>
       </c>
       <c r="Q6" s="5" t="s">
